--- a/docs/IPCse_informe.xlsx
+++ b/docs/IPCse_informe.xlsx
@@ -428,10 +428,10 @@
         <v>2026</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -586,32 +586,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Abr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Abr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jul</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Ago</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ago</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -652,25 +652,25 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="G49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I49" t="n">
         <v>2.4</v>
       </c>
-      <c r="H49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.1</v>
-      </c>
       <c r="J49" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="K49" t="n">
         <v>1.8</v>
       </c>
       <c r="L49" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="50">
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H50" t="n">
         <v>2.5</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>2.8</v>
       </c>
-      <c r="I50" t="n">
-        <v>2.5</v>
-      </c>
       <c r="J50" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K50" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L50" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="51">
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G51" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I51" t="n">
         <v>2.5</v>
       </c>
-      <c r="I51" t="n">
-        <v>2.6</v>
-      </c>
       <c r="J51" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="K51" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L51" t="n">
         <v>33.1</v>
@@ -736,25 +736,25 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="G52" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H52" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="K52" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L52" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="53">
@@ -764,25 +764,25 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="G53" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="H53" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="K53" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="L53" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="54">
@@ -792,25 +792,25 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G54" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="H54" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K54" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="L54" t="n">
-        <v>33.4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -820,25 +820,25 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G55" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H55" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="K55" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="L55" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="56">
@@ -848,25 +848,25 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="G56" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
-        <v>1.7</v>
-      </c>
       <c r="L56" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="57">
@@ -876,25 +876,25 @@
         </is>
       </c>
       <c r="F57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H57" t="n">
         <v>2.1</v>
       </c>
-      <c r="G57" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.8</v>
-      </c>
       <c r="I57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J57" t="n">
         <v>2.1</v>
       </c>
-      <c r="J57" t="n">
-        <v>1.5</v>
-      </c>
       <c r="K57" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="L57" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="58">
@@ -904,25 +904,25 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="H58" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9</v>
+        <v>-1</v>
       </c>
       <c r="L58" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="59">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G59" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H59" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="K59" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="L59" t="n">
         <v>49.1</v>
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="G60" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="H60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J60" t="n">
         <v>1.4</v>
       </c>
-      <c r="I60" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2.1</v>
-      </c>
       <c r="K60" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="L60" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="61">
@@ -988,25 +988,25 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G61" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="H61" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="K61" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="L61" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="62">
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G62" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K62" t="n">
         <v>1.5</v>
       </c>
       <c r="L62" t="n">
-        <v>38.2</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="63">
@@ -1044,25 +1044,25 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="G63" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H63" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K63" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="L63" t="n">
-        <v>36.8</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="64">
@@ -1072,25 +1072,25 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="H64" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>5</v>
+        <v>-0</v>
       </c>
       <c r="K64" t="n">
-        <v>-0</v>
+        <v>1.9</v>
       </c>
       <c r="L64" t="n">
-        <v>31.5</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="65">
@@ -1100,25 +1100,25 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>-4.7</v>
+        <v>5.6</v>
       </c>
       <c r="G65" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="H65" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K65" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="L65" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="66">
@@ -1128,22 +1128,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="G66" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="H66" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J66" t="n">
         <v>1.8</v>
       </c>
-      <c r="I66" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J66" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K66" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="L66" t="n">
         <v>34.6</v>
@@ -1156,25 +1156,25 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="G67" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H67" t="n">
         <v>3.1</v>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="K67" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="L67" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="68">
@@ -1184,22 +1184,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="G68" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="H68" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="K68" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L68" t="n">
         <v>30.1</v>
@@ -1212,25 +1212,25 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G69" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I69" t="n">
         <v>3</v>
       </c>
-      <c r="I69" t="n">
-        <v>2.5</v>
-      </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="K69" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L69" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="70">
@@ -1240,25 +1240,25 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="G70" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="H70" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I70" t="n">
         <v>2.7</v>
       </c>
       <c r="J70" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="K70" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="L70" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="71">
@@ -1268,25 +1268,25 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="G71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J71" t="n">
         <v>1.6</v>
       </c>
-      <c r="H71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K71" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="L71" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="72">
@@ -1296,25 +1296,25 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="G72" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="H72" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K72" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L72" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="73">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="F73" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G73" t="n">
         <v>2.1</v>
       </c>
-      <c r="G73" t="n">
-        <v>1.2</v>
-      </c>
       <c r="H73" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="K73" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L73" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
@@ -1352,25 +1352,25 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="G74" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="H74" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="I74" t="n">
         <v>2.2</v>
       </c>
       <c r="J74" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="K74" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="L74" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
     </row>
   </sheetData>
@@ -1436,25 +1436,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="G15" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="H15" t="n">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="J15" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="K15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="18">
@@ -1464,25 +1464,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="F18" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="G18" t="n">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="H18" t="n">
-        <v>0.76</v>
+        <v>0.17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="J18" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="K18" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="19">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20">
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="F20" t="n">
-        <v>0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="G20" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.18</v>
+        <v>-0.04</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1548,25 +1548,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="F21" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="I21" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="J21" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="22">
@@ -1576,25 +1576,25 @@
         </is>
       </c>
       <c r="E22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>0.08</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.05</v>
-      </c>
       <c r="I22" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.06</v>
+        <v>-0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="23">
@@ -1604,25 +1604,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="F23" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G23" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H23" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="J23" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="K23" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="24">
@@ -1632,22 +1632,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F24" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J24" t="n">
         <v>0.16</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.31</v>
       </c>
       <c r="K24" t="n">
         <v>0.18</v>
@@ -1669,7 +1669,7 @@
         <v>0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I25" t="n">
         <v>0.06</v>
@@ -1678,7 +1678,7 @@
         <v>0.06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1688,25 +1688,25 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.04</v>
+        <v>0.15</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.01</v>
+        <v>0.2</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="K26" t="n">
-        <v>-0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="27">
@@ -1716,25 +1716,25 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="H27" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I27" t="n">
         <v>0.04</v>
       </c>
       <c r="J27" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="K27" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
@@ -1744,25 +1744,25 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="F28" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="G28" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.18</v>
       </c>
-      <c r="I28" t="n">
-        <v>0.01</v>
-      </c>
       <c r="J28" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="29">
@@ -1772,25 +1772,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="G29" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J29" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
@@ -1800,25 +1800,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33.66</v>
+        <v>33.54</v>
       </c>
       <c r="F32" t="n">
-        <v>33.12</v>
+        <v>33.06</v>
       </c>
       <c r="G32" t="n">
-        <v>34</v>
+        <v>33.59</v>
       </c>
       <c r="H32" t="n">
-        <v>36.99</v>
+        <v>36.86</v>
       </c>
       <c r="I32" t="n">
-        <v>33.4</v>
+        <v>33.03</v>
       </c>
       <c r="J32" t="n">
-        <v>31.6</v>
+        <v>30.29</v>
       </c>
       <c r="K32" t="n">
-        <v>33.47</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="35">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8.6</v>
+        <v>8.68</v>
       </c>
       <c r="F35" t="n">
-        <v>10.62</v>
+        <v>10.71</v>
       </c>
       <c r="G35" t="n">
-        <v>13.06</v>
+        <v>12.83</v>
       </c>
       <c r="H35" t="n">
-        <v>14.98</v>
+        <v>14.64</v>
       </c>
       <c r="I35" t="n">
-        <v>10.47</v>
+        <v>10.39</v>
       </c>
       <c r="J35" t="n">
-        <v>8.52</v>
+        <v>8.42</v>
       </c>
       <c r="K35" t="n">
-        <v>9.94</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F36" t="n">
         <v>0.63</v>
       </c>
       <c r="G36" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="H36" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="I36" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="J36" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="K36" t="n">
         <v>0.59</v>
@@ -1884,25 +1884,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="F37" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="G37" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H37" t="n">
-        <v>1.05</v>
+        <v>0.87</v>
       </c>
       <c r="I37" t="n">
         <v>1.29</v>
       </c>
       <c r="J37" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="K37" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="38">
@@ -1912,25 +1912,25 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="F38" t="n">
-        <v>4.1</v>
+        <v>4.17</v>
       </c>
       <c r="G38" t="n">
-        <v>4.64</v>
+        <v>4.81</v>
       </c>
       <c r="H38" t="n">
-        <v>7.63</v>
+        <v>7.94</v>
       </c>
       <c r="I38" t="n">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="J38" t="n">
-        <v>6.16</v>
+        <v>5.96</v>
       </c>
       <c r="K38" t="n">
-        <v>4.67</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="39">
@@ -1940,25 +1940,25 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="F39" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G39" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H39" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="J39" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="K39" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="40">
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="F40" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="G40" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H40" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="I40" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="J40" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="41">
@@ -1996,25 +1996,25 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="F41" t="n">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="G41" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="H41" t="n">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="I41" t="n">
-        <v>5.39</v>
+        <v>5.3</v>
       </c>
       <c r="J41" t="n">
-        <v>5.63</v>
+        <v>5.05</v>
       </c>
       <c r="K41" t="n">
-        <v>4.27</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="42">
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="F42" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H42" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.88</v>
       </c>
       <c r="I42" t="n">
         <v>0.74</v>
@@ -2042,7 +2042,7 @@
         <v>0.86</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="43">
@@ -2052,25 +2052,25 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="F43" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="G43" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H43" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="I43" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J43" t="n">
         <v>1.65</v>
       </c>
-      <c r="J43" t="n">
-        <v>1.62</v>
-      </c>
       <c r="K43" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="44">
@@ -2080,22 +2080,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="F44" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="G44" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="H44" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="I44" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="J44" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="K44" t="n">
         <v>0.83</v>
@@ -2108,25 +2108,25 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4.56</v>
+        <v>4.62</v>
       </c>
       <c r="F45" t="n">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="G45" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="H45" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="I45" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="J45" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="K45" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="46">
@@ -2136,25 +2136,25 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="F46" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="G46" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H46" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H46" t="n">
-        <v>0.9</v>
-      </c>
       <c r="I46" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="K46" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="50">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.741</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="52">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.079</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="53">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.098</v>
+        <v>-0.112</v>
       </c>
     </row>
     <row r="54">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.115</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="55">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-0.002</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="56">
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.314</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="57">
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.128</v>
+        <v>0.073</v>
       </c>
     </row>
   </sheetData>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="49">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="52">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="54">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="55">
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="56">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="57">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="58">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="59">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="60">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="61">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="63">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="67">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="68">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>-0.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="69">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="70">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="71">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="72">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="73">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="74">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="76">
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="79">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="80">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>-0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="81">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>-0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="82">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="84">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="85">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="86">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="87">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -2863,7 +2863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4510,6 +4510,20 @@
       </c>
       <c r="D117" t="n">
         <v>1.4739625533</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1.9336102032</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.7328801255</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.414705568</v>
       </c>
     </row>
   </sheetData>
@@ -4545,10 +4559,10 @@
     </row>
     <row r="7">
       <c r="M7" s="1" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="N7" t="n">
-        <v>2.0113765571</v>
+        <v>1.8570561152</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -4558,10 +4572,10 @@
     </row>
     <row r="8">
       <c r="M8" s="1" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="N8" t="n">
-        <v>1.8570561152</v>
+        <v>2.205178034</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -4571,10 +4585,10 @@
     </row>
     <row r="9">
       <c r="M9" s="1" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="N9" t="n">
-        <v>2.205178034</v>
+        <v>2.4043447382</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -4584,10 +4598,10 @@
     </row>
     <row r="10">
       <c r="M10" s="1" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4043447382</v>
+        <v>2.8408216937</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -4597,10 +4611,10 @@
     </row>
     <row r="11">
       <c r="M11" s="1" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8408216937</v>
+        <v>3.0907918175</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -4610,10 +4624,10 @@
     </row>
     <row r="12">
       <c r="M12" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9550355818</v>
+        <v>3.0419120595</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -4623,10 +4637,10 @@
     </row>
     <row r="13">
       <c r="M13" s="1" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0470422621</v>
+        <v>2.8225733309</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -4636,10 +4650,10 @@
     </row>
     <row r="14">
       <c r="M14" s="1" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8142494324</v>
+        <v>2.4477242709</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -4649,10 +4663,10 @@
     </row>
     <row r="15">
       <c r="M15" s="1" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4534031705</v>
+        <v>2.2818175995</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -4662,10 +4676,10 @@
     </row>
     <row r="16">
       <c r="M16" s="1" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2867341419</v>
+        <v>2.0888642225</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -4675,10 +4689,10 @@
     </row>
     <row r="17">
       <c r="M17" s="1" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="N17" t="n">
-        <v>2.0916787763</v>
+        <v>2.3584610385</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -4688,10 +4702,10 @@
     </row>
     <row r="18">
       <c r="M18" s="1" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3756256463</v>
+        <v>1.7575130529</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -4701,10 +4715,10 @@
     </row>
     <row r="19">
       <c r="M19" s="1" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="N19" t="n">
-        <v>1.776385833</v>
+        <v>1.7519381465</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -4714,10 +4728,10 @@
     </row>
     <row r="20">
       <c r="M20" s="1" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="N20" t="n">
-        <v>1.6880285949</v>
+        <v>1.3854144546</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -4727,10 +4741,10 @@
     </row>
     <row r="21">
       <c r="M21" s="1" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="N21" t="n">
-        <v>1.3854144546</v>
+        <v>1.9924010965</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -4740,10 +4754,10 @@
     </row>
     <row r="22">
       <c r="M22" s="1" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="N22" t="n">
-        <v>1.9924010965</v>
+        <v>2.1860871225</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4753,10 +4767,10 @@
     </row>
     <row r="23">
       <c r="M23" s="1" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1860871225</v>
+        <v>2.6573301235</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4766,10 +4780,10 @@
     </row>
     <row r="24">
       <c r="M24" s="1" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6573301235</v>
+        <v>3.3671413763</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4779,10 +4793,10 @@
     </row>
     <row r="25">
       <c r="M25" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3671413763</v>
+        <v>2.724826202</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4792,10 +4806,10 @@
     </row>
     <row r="26">
       <c r="M26" s="1" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="N26" t="n">
-        <v>2.724826202</v>
+        <v>2.6986459997</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4805,10 +4819,10 @@
     </row>
     <row r="27">
       <c r="M27" s="1" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6986459997</v>
+        <v>1.7446210868</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4818,10 +4832,10 @@
     </row>
     <row r="28">
       <c r="M28" s="1" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="N28" t="n">
-        <v>1.7446210868</v>
+        <v>2.1608535554</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4831,10 +4845,10 @@
     </row>
     <row r="29">
       <c r="M29" s="1" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="N29" t="n">
-        <v>2.1608535554</v>
+        <v>1.8488507159</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4844,10 +4858,10 @@
     </row>
     <row r="30">
       <c r="M30" s="1" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="N30" t="n">
-        <v>1.8488507159</v>
+        <v>2.3473611387</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4857,10 +4871,10 @@
     </row>
     <row r="31">
       <c r="M31" s="1" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="N31" t="n">
-        <v>2.3473611387</v>
+        <v>1.4739625533</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4870,10 +4884,10 @@
     </row>
     <row r="32">
       <c r="M32" s="1" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="N32" t="n">
-        <v>1.4739625533</v>
+        <v>1.414705568</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
